--- a/Redes.xlsx
+++ b/Redes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alan Chaires\Documents\Dirección de Planeación, Evaluación e Innovación\9- Tablero Redes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8893714-069E-400A-8939-6B56755D8F5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD10E159-0572-4354-8D06-A239D642DD5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{7FB54C1C-01EA-46D2-B3AA-10A0B7D9ACCD}"/>
+    <workbookView xWindow="3195" yWindow="3195" windowWidth="21510" windowHeight="7845" firstSheet="1" activeTab="3" xr2:uid="{7FB54C1C-01EA-46D2-B3AA-10A0B7D9ACCD}"/>
   </bookViews>
   <sheets>
     <sheet name="01_Resumen" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="108">
   <si>
     <t>Fecha_reporte</t>
   </si>
@@ -250,9 +250,6 @@
   </si>
   <si>
     <t>archivo_imagen</t>
-  </si>
-  <si>
-    <t>27082026_101.png</t>
   </si>
   <si>
     <t>texto</t>
@@ -405,6 +402,12 @@
   <si>
     <t>Nos llegaron aparatos de movilidad, sillas de ruedas, bastones, camas de hospital, sillas para bañar, etcétera… Por favor, si conoces a alguien que los necesite compárteme los datos para hacérselos llegar. 👇👇
 #AyudarEsLaNuevaRuta #OSC #IgualdadEInclusión</t>
+  </si>
+  <si>
+    <t>27082026_006.pmg</t>
+  </si>
+  <si>
+    <t>27082026_019.png</t>
   </si>
 </sst>
 </file>
@@ -958,7 +961,7 @@
         <v>50</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H2" s="5">
         <v>1400</v>
@@ -992,7 +995,7 @@
         <v>29</v>
       </c>
       <c r="G3" s="12" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H3" s="5">
         <v>569</v>
@@ -1005,7 +1008,7 @@
       </c>
       <c r="K3" s="5"/>
       <c r="M3" s="8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="39">
@@ -1028,7 +1031,7 @@
         <v>29</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H4" s="5">
         <v>414</v>
@@ -1041,7 +1044,7 @@
       </c>
       <c r="K4" s="5"/>
       <c r="M4" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="78">
@@ -1064,7 +1067,7 @@
         <v>52</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H5" s="5">
         <v>337</v>
@@ -1077,7 +1080,7 @@
       </c>
       <c r="K5" s="5"/>
       <c r="M5" s="8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="39">
@@ -1100,7 +1103,7 @@
         <v>51</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H6" s="5">
         <v>167</v>
@@ -1113,7 +1116,7 @@
       </c>
       <c r="K6" s="5"/>
       <c r="M6" s="7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="19.5">
@@ -1211,7 +1214,7 @@
         <v>49</v>
       </c>
       <c r="G10" s="14" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H10" s="5"/>
       <c r="I10" s="5"/>
@@ -1238,7 +1241,7 @@
         <v>29</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H11" s="5">
         <v>100</v>
@@ -1253,7 +1256,7 @@
         <v>2</v>
       </c>
       <c r="M11" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="58.5">
@@ -1276,7 +1279,7 @@
         <v>52</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H12" s="5">
         <v>66</v>
@@ -1289,7 +1292,7 @@
       </c>
       <c r="K12" s="5"/>
       <c r="M12" s="7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="20.25">
@@ -1312,7 +1315,7 @@
         <v>51</v>
       </c>
       <c r="G13" s="13" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H13" s="5">
         <v>58</v>
@@ -1327,7 +1330,7 @@
         <v>1</v>
       </c>
       <c r="M13" s="8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="19.5">
@@ -1350,7 +1353,7 @@
         <v>31</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H14" s="5">
         <v>223</v>
@@ -1363,7 +1366,7 @@
       </c>
       <c r="K14" s="5"/>
       <c r="M14" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="19.5">
@@ -1386,7 +1389,7 @@
         <v>29</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H15" s="5">
         <v>185</v>
@@ -1399,7 +1402,7 @@
       </c>
       <c r="K15" s="18"/>
       <c r="M15" s="8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="58.5">
@@ -1422,7 +1425,7 @@
         <v>29</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H16" s="5">
         <v>131</v>
@@ -1435,7 +1438,7 @@
       </c>
       <c r="K16" s="18"/>
       <c r="M16" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="117">
@@ -1458,7 +1461,7 @@
         <v>28</v>
       </c>
       <c r="G17" s="11" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H17" s="5">
         <v>29</v>
@@ -1471,7 +1474,7 @@
       </c>
       <c r="K17" s="18"/>
       <c r="M17" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="39">
@@ -1494,7 +1497,7 @@
         <v>30</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H18" s="5">
         <v>25</v>
@@ -1507,7 +1510,7 @@
       </c>
       <c r="K18" s="18"/>
       <c r="M18" s="8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="58.5">
@@ -1530,7 +1533,7 @@
         <v>24</v>
       </c>
       <c r="G19" s="11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H19" s="5">
         <v>19</v>
@@ -1543,7 +1546,7 @@
       </c>
       <c r="K19" s="5"/>
       <c r="M19" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="58.5">
@@ -1566,7 +1569,7 @@
         <v>29</v>
       </c>
       <c r="G20" s="11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H20" s="5">
         <v>35</v>
@@ -1579,7 +1582,7 @@
         <v>4</v>
       </c>
       <c r="M20" s="8" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="39">
@@ -1602,7 +1605,7 @@
         <v>30</v>
       </c>
       <c r="G21" s="11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H21" s="5">
         <v>32</v>
@@ -1617,7 +1620,7 @@
         <v>1</v>
       </c>
       <c r="M21" s="8" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="19.5">
@@ -1640,7 +1643,7 @@
         <v>31</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H22" s="5">
         <v>22</v>
@@ -1649,7 +1652,7 @@
       <c r="J22" s="5"/>
       <c r="K22" s="5"/>
       <c r="M22" s="8" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="58.5">
@@ -1672,7 +1675,7 @@
         <v>24</v>
       </c>
       <c r="G23" s="11" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H23" s="5">
         <v>16</v>
@@ -1685,7 +1688,7 @@
         <v>1</v>
       </c>
       <c r="M23" s="8" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="19.5">
@@ -1891,7 +1894,7 @@
         <v>68</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G1" s="4" t="s">
         <v>69</v>
@@ -1911,10 +1914,10 @@
         <v>38</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>70</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="19.5">
@@ -1931,10 +1934,10 @@
         <v>57</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>70</v>
+        <v>107</v>
       </c>
     </row>
   </sheetData>

--- a/Redes.xlsx
+++ b/Redes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alan Chaires\Documents\Dirección de Planeación, Evaluación e Innovación\9- Tablero Redes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD10E159-0572-4354-8D06-A239D642DD5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A992B8A-F097-4212-9447-A32A4E9C62F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3195" yWindow="3195" windowWidth="21510" windowHeight="7845" firstSheet="1" activeTab="3" xr2:uid="{7FB54C1C-01EA-46D2-B3AA-10A0B7D9ACCD}"/>
+    <workbookView xWindow="3195" yWindow="3195" windowWidth="21510" windowHeight="7845" xr2:uid="{7FB54C1C-01EA-46D2-B3AA-10A0B7D9ACCD}"/>
   </bookViews>
   <sheets>
     <sheet name="01_Resumen" sheetId="1" r:id="rId1"/>
@@ -404,10 +404,10 @@
 #AyudarEsLaNuevaRuta #OSC #IgualdadEInclusión</t>
   </si>
   <si>
-    <t>27082026_006.pmg</t>
-  </si>
-  <si>
     <t>27082026_019.png</t>
+  </si>
+  <si>
+    <t>27082026_006.png</t>
   </si>
 </sst>
 </file>
@@ -844,6 +844,8 @@
   <cols>
     <col min="1" max="1" width="18.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="33.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="33.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -1917,7 +1919,7 @@
         <v>88</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="19.5">
@@ -1937,7 +1939,7 @@
         <v>105</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>

--- a/Redes.xlsx
+++ b/Redes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alan Chaires\Documents\Dirección de Planeación, Evaluación e Innovación\9- Tablero Redes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A992B8A-F097-4212-9447-A32A4E9C62F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8446CECA-3524-4760-88F7-BB0AC5414FA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3195" yWindow="3195" windowWidth="21510" windowHeight="7845" xr2:uid="{7FB54C1C-01EA-46D2-B3AA-10A0B7D9ACCD}"/>
   </bookViews>
@@ -42,9 +42,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="108">
   <si>
-    <t>Fecha_reporte</t>
-  </si>
-  <si>
     <t>Responsable</t>
   </si>
   <si>
@@ -52,9 +49,6 @@
   </si>
   <si>
     <t>Observaciones</t>
-  </si>
-  <si>
-    <t>Fecha_actualización</t>
   </si>
   <si>
     <t>DPEI</t>
@@ -408,6 +402,12 @@
   </si>
   <si>
     <t>27082026_006.png</t>
+  </si>
+  <si>
+    <t>fecha_actualizacion</t>
+  </si>
+  <si>
+    <t>fecha_reporte</t>
   </si>
 </sst>
 </file>
@@ -850,19 +850,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="E1" s="2" t="s">
-        <v>4</v>
+        <v>106</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -870,13 +870,13 @@
         <v>46262</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>5</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>7</v>
       </c>
       <c r="E2" s="3">
         <v>46261</v>
@@ -904,66 +904,66 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="D1" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="E1" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="F1" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="G1" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="H1" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="I1" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="J1" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="K1" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="L1" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="M1" s="8" t="s">
         <v>18</v>
-      </c>
-      <c r="L1" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="M1" s="8" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="19.5">
       <c r="A2" s="8" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B2" s="10">
         <v>46261</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="H2" s="5">
         <v>1400</v>
@@ -974,30 +974,30 @@
       <c r="J2" s="5"/>
       <c r="K2" s="5"/>
       <c r="M2" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="20.25">
       <c r="A3" s="8" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B3" s="10">
         <v>46261</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E3" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F3" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="F3" s="5" t="s">
-        <v>29</v>
-      </c>
       <c r="G3" s="12" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H3" s="5">
         <v>569</v>
@@ -1010,30 +1010,30 @@
       </c>
       <c r="K3" s="5"/>
       <c r="M3" s="8" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="39">
       <c r="A4" s="8" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B4" s="10">
         <v>46261</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E4" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="F4" s="5" t="s">
-        <v>29</v>
-      </c>
       <c r="G4" s="11" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H4" s="5">
         <v>414</v>
@@ -1046,30 +1046,30 @@
       </c>
       <c r="K4" s="5"/>
       <c r="M4" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="78">
       <c r="A5" s="8" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B5" s="10">
         <v>46261</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="H5" s="5">
         <v>337</v>
@@ -1082,30 +1082,30 @@
       </c>
       <c r="K5" s="5"/>
       <c r="M5" s="8" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="39">
       <c r="A6" s="8" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B6" s="10">
         <v>46261</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H6" s="5">
         <v>167</v>
@@ -1118,27 +1118,27 @@
       </c>
       <c r="K6" s="5"/>
       <c r="M6" s="7" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="19.5">
       <c r="A7" s="8" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B7" s="10">
         <v>46261</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G7" s="6"/>
       <c r="H7" s="5"/>
@@ -1148,22 +1148,22 @@
     </row>
     <row r="8" spans="1:13" ht="19.5">
       <c r="A8" s="8" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B8" s="10">
         <v>46261</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G8" s="6"/>
       <c r="H8" s="5"/>
@@ -1173,22 +1173,22 @@
     </row>
     <row r="9" spans="1:13" ht="19.5">
       <c r="A9" s="8" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B9" s="10">
         <v>46261</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G9" s="6"/>
       <c r="H9" s="5"/>
@@ -1198,25 +1198,25 @@
     </row>
     <row r="10" spans="1:13" ht="20.25">
       <c r="A10" s="8" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B10" s="10">
         <v>46261</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G10" s="14" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="H10" s="5"/>
       <c r="I10" s="5"/>
@@ -1225,25 +1225,25 @@
     </row>
     <row r="11" spans="1:13" ht="39">
       <c r="A11" s="8" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B11" s="10">
         <v>46261</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E11" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F11" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="F11" s="5" t="s">
-        <v>29</v>
-      </c>
       <c r="G11" s="11" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H11" s="5">
         <v>100</v>
@@ -1258,30 +1258,30 @@
         <v>2</v>
       </c>
       <c r="M11" s="7" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="58.5">
       <c r="A12" s="8" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B12" s="10">
         <v>46261</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="H12" s="5">
         <v>66</v>
@@ -1294,30 +1294,30 @@
       </c>
       <c r="K12" s="5"/>
       <c r="M12" s="7" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="20.25">
       <c r="A13" s="8" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B13" s="10">
         <v>46261</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G13" s="13" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H13" s="5">
         <v>58</v>
@@ -1332,30 +1332,30 @@
         <v>1</v>
       </c>
       <c r="M13" s="8" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="19.5">
       <c r="A14" s="8" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B14" s="10">
         <v>46261</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="H14" s="5">
         <v>223</v>
@@ -1368,30 +1368,30 @@
       </c>
       <c r="K14" s="5"/>
       <c r="M14" s="8" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="19.5">
       <c r="A15" s="8" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B15" s="10">
         <v>46261</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H15" s="5">
         <v>185</v>
@@ -1404,30 +1404,30 @@
       </c>
       <c r="K15" s="18"/>
       <c r="M15" s="8" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="58.5">
       <c r="A16" s="8" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B16" s="10">
         <v>46261</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E16" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F16" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="F16" s="5" t="s">
-        <v>29</v>
-      </c>
       <c r="G16" s="11" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="H16" s="5">
         <v>131</v>
@@ -1440,30 +1440,30 @@
       </c>
       <c r="K16" s="18"/>
       <c r="M16" s="8" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="117">
       <c r="A17" s="8" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B17" s="10">
         <v>46261</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G17" s="11" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="H17" s="5">
         <v>29</v>
@@ -1476,30 +1476,30 @@
       </c>
       <c r="K17" s="18"/>
       <c r="M17" s="8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="39">
       <c r="A18" s="8" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B18" s="10">
         <v>46261</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H18" s="5">
         <v>25</v>
@@ -1512,30 +1512,30 @@
       </c>
       <c r="K18" s="18"/>
       <c r="M18" s="8" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="58.5">
       <c r="A19" s="8" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B19" s="10">
         <v>46261</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D19" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F19" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="E19" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="F19" s="5" t="s">
-        <v>24</v>
-      </c>
       <c r="G19" s="11" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="H19" s="5">
         <v>19</v>
@@ -1548,30 +1548,30 @@
       </c>
       <c r="K19" s="5"/>
       <c r="M19" s="8" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="58.5">
       <c r="A20" s="8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B20" s="10">
         <v>46261</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E20" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F20" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="F20" s="5" t="s">
-        <v>29</v>
-      </c>
       <c r="G20" s="11" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H20" s="5">
         <v>35</v>
@@ -1584,30 +1584,30 @@
         <v>4</v>
       </c>
       <c r="M20" s="8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="39">
       <c r="A21" s="8" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B21" s="10">
         <v>46261</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G21" s="11" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="H21" s="5">
         <v>32</v>
@@ -1622,30 +1622,30 @@
         <v>1</v>
       </c>
       <c r="M21" s="8" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="19.5">
       <c r="A22" s="8" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B22" s="10">
         <v>46261</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H22" s="5">
         <v>22</v>
@@ -1654,30 +1654,30 @@
       <c r="J22" s="5"/>
       <c r="K22" s="5"/>
       <c r="M22" s="8" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="58.5">
       <c r="A23" s="8" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B23" s="10">
         <v>46261</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G23" s="11" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="H23" s="5">
         <v>16</v>
@@ -1690,27 +1690,27 @@
         <v>1</v>
       </c>
       <c r="M23" s="8" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="19.5">
       <c r="A24" s="8" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B24" s="10">
         <v>46261</v>
       </c>
       <c r="C24" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E24" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="D24" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>23</v>
-      </c>
       <c r="F24" s="5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G24" s="6"/>
       <c r="H24" s="5"/>
@@ -1720,22 +1720,22 @@
     </row>
     <row r="25" spans="1:13" ht="19.5">
       <c r="A25" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B25" s="10">
         <v>46261</v>
       </c>
       <c r="C25" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E25" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="D25" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>23</v>
-      </c>
       <c r="F25" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G25" s="6"/>
       <c r="H25" s="5"/>
@@ -1745,22 +1745,22 @@
     </row>
     <row r="26" spans="1:13" ht="19.5">
       <c r="A26" s="8" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B26" s="10">
         <v>46261</v>
       </c>
       <c r="C26" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E26" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>23</v>
-      </c>
       <c r="F26" s="5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G26" s="6"/>
       <c r="H26" s="5"/>
@@ -1791,19 +1791,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" t="s">
         <v>9</v>
       </c>
-      <c r="B1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C1" t="s">
-        <v>11</v>
-      </c>
       <c r="D1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="19.5">
@@ -1811,10 +1811,10 @@
         <v>46261</v>
       </c>
       <c r="B2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D2" s="5">
         <v>205000</v>
@@ -1825,10 +1825,10 @@
         <v>46261</v>
       </c>
       <c r="B3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D3" s="5">
         <v>17300</v>
@@ -1839,10 +1839,10 @@
         <v>46261</v>
       </c>
       <c r="B4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D4" s="5">
         <v>234000</v>
@@ -1853,10 +1853,10 @@
         <v>46261</v>
       </c>
       <c r="B5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D5" s="5">
         <v>39900</v>
@@ -1881,25 +1881,25 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>11</v>
-      </c>
       <c r="D1" s="4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E1" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="F1" s="4" t="s">
-        <v>70</v>
-      </c>
       <c r="G1" s="4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="19.5">
@@ -1907,19 +1907,19 @@
         <v>46261</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C2" s="16" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="19.5">
@@ -1927,19 +1927,19 @@
         <v>46261</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C3" s="16" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>

--- a/Redes.xlsx
+++ b/Redes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alan Chaires\Documents\Dirección de Planeación, Evaluación e Innovación\9- Tablero Redes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8446CECA-3524-4760-88F7-BB0AC5414FA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC32EC30-E551-4709-A334-B8F4992A1534}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3195" yWindow="3195" windowWidth="21510" windowHeight="7845" xr2:uid="{7FB54C1C-01EA-46D2-B3AA-10A0B7D9ACCD}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{7FB54C1C-01EA-46D2-B3AA-10A0B7D9ACCD}"/>
   </bookViews>
   <sheets>
     <sheet name="01_Resumen" sheetId="1" r:id="rId1"/>
@@ -945,7 +945,7 @@
     </row>
     <row r="2" spans="1:13" ht="19.5">
       <c r="A2" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B2" s="10">
         <v>46261</v>
@@ -1198,7 +1198,7 @@
     </row>
     <row r="10" spans="1:13" ht="20.25">
       <c r="A10" s="8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B10" s="10">
         <v>46261</v>
